--- a/data/trans_dic/P37A$medicootras-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicootras-Edad-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,67</t>
+          <t>0,24; 2,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,59</t>
+          <t>0,35; 2,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,34</t>
+          <t>0,24; 2,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,53</t>
+          <t>0,25; 1,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,04</t>
+          <t>0,48; 1,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,26</t>
+          <t>0,26; 2,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,36</t>
+          <t>0,23; 3,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,12</t>
+          <t>0,31; 2,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,15</t>
+          <t>0,15; 1,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,88</t>
+          <t>1,1; 4,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,68</t>
+          <t>0,07; 0,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,65</t>
+          <t>0,43; 1,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,92</t>
+          <t>0,16; 1,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,06</t>
+          <t>0,94; 3,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,0</t>
+          <t>0,11; 1,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,15</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,19</t>
+          <t>0,14; 1,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,9</t>
+          <t>0,41; 1,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,06</t>
+          <t>0,4; 2,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,61</t>
+          <t>0,86; 2,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,66</t>
+          <t>0,07; 0,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,25</t>
+          <t>0,27; 1,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,43</t>
+          <t>0,36; 1,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,4</t>
+          <t>0,45; 1,45</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1137,32 +1137,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,07</t>
+          <t>0,18; 2,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,77</t>
+          <t>0,3; 1,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,6</t>
+          <t>0,17; 1,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,57</t>
+          <t>0,47; 1,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,15</t>
+          <t>0,16; 1,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,96</t>
+          <t>0,17; 0,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,2</t>
+          <t>0,31; 1,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,82</t>
+          <t>0,34; 1,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1282,57 +1282,57 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,48</t>
+          <t>0,49; 2,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,1</t>
+          <t>0,45; 3,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,0</t>
+          <t>0,22; 1,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,97</t>
+          <t>1,22; 3,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,95</t>
+          <t>0,35; 1,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,12</t>
+          <t>0,11; 1,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,36</t>
+          <t>1,05; 2,32</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,33</t>
+          <t>0,27; 2,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,28</t>
+          <t>0,72; 3,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,59</t>
+          <t>0,54; 2,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,97</t>
+          <t>0,27; 1,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,91</t>
+          <t>0,78; 2,17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1562,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,36</t>
+          <t>0,37; 1,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,53</t>
+          <t>0,18; 1,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,99</t>
+          <t>0,23; 1,14</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,44</t>
+          <t>0,09; 0,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,82</t>
+          <t>0,29; 0,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,95</t>
+          <t>0,37; 0,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,95</t>
+          <t>0,41; 1,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,45</t>
+          <t>0,1; 0,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,12</t>
+          <t>0,48; 1,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,97</t>
+          <t>0,41; 0,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,52</t>
+          <t>1,02; 1,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,37</t>
+          <t>0,13; 0,38</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,84</t>
+          <t>0,45; 0,85</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,84</t>
+          <t>0,46; 0,85</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,13</t>
+          <t>0,8; 1,24</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4752</t>
+          <t>0; 4032</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1055; 12118</t>
+          <t>1074; 11308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1062; 10859</t>
+          <t>1464; 12069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7343</t>
+          <t>0; 7538</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>943; 9248</t>
+          <t>935; 9008</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4781</t>
+          <t>0; 4784</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2422; 13514</t>
+          <t>2253; 13236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3871; 16590</t>
+          <t>3907; 15353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16349</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5244</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1789; 15496</t>
+          <t>1805; 15101</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7600</t>
+          <t>0; 6934</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1081; 18446</t>
+          <t>1091; 14829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7702</t>
+          <t>0; 7065</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1840; 12964</t>
+          <t>1897; 13082</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>841; 6479</t>
+          <t>848; 7811</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4984; 19891</t>
+          <t>5500; 20352</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>980; 9283</t>
+          <t>977; 8397</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5634; 21342</t>
+          <t>5534; 22518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1760; 10642</t>
+          <t>1800; 12072</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8657; 28641</t>
+          <t>9170; 30592</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10802</t>
         </is>
       </c>
     </row>
@@ -2489,57 +2489,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>713; 6852</t>
+          <t>717; 7177</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>898; 11177</t>
+          <t>902; 11186</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 813</t>
+          <t>0; 6963</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>955; 8182</t>
+          <t>960; 8023</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2891; 13535</t>
+          <t>2934; 13839</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2721; 13648</t>
+          <t>2653; 14408</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5119; 15427</t>
+          <t>5385; 16153</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>954; 8797</t>
+          <t>959; 8218</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4799; 17396</t>
+          <t>3813; 17721</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5373; 19048</t>
+          <t>4824; 20601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5066; 15816</t>
+          <t>5629; 18087</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>9419</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>908; 10752</t>
+          <t>918; 10805</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5159</t>
+          <t>0; 5202</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1975; 11465</t>
+          <t>1963; 11443</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6416</t>
+          <t>0; 7503</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4929</t>
+          <t>0; 5843</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1068; 9884</t>
+          <t>1074; 10869</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>993; 8419</t>
+          <t>1001; 8438</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3113; 11164</t>
+          <t>3451; 12509</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1682; 11918</t>
+          <t>1692; 12546</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2081; 11808</t>
+          <t>2118; 11931</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3885; 15598</t>
+          <t>4032; 15618</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3415; 13163</t>
+          <t>4911; 15814</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>19439</t>
         </is>
       </c>
     </row>
@@ -2905,57 +2905,57 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7356</t>
+          <t>0; 6383</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6010</t>
+          <t>0; 6836</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2963; 13900</t>
+          <t>2989; 14772</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5774</t>
+          <t>0; 5114</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1124; 13860</t>
+          <t>2001; 14188</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1092; 9912</t>
+          <t>1087; 8814</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6308; 16274</t>
+          <t>7437; 18509</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5145</t>
+          <t>0; 5678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3112; 17097</t>
+          <t>3067; 16648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1108; 10953</t>
+          <t>1117; 10860</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11346; 26200</t>
+          <t>12837; 28247</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11986</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5371</t>
+          <t>0; 6186</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>895; 7794</t>
+          <t>905; 8098</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2999; 12089</t>
+          <t>2920; 13350</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3138,17 +3138,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 10698</t>
+          <t>0; 10364</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1342; 9685</t>
+          <t>2385; 9052</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5381</t>
+          <t>0; 6266</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1944; 14039</t>
+          <t>1932; 13354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5045; 18694</t>
+          <t>6571; 18328</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>601</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>4329</t>
         </is>
       </c>
     </row>
@@ -3321,17 +3321,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5879</t>
+          <t>0; 7056</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4093</t>
+          <t>0; 5085</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3631</t>
+          <t>0; 3577</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 7898</t>
+          <t>0; 8018</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>864; 5789</t>
+          <t>1710; 7466</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3361,17 +3361,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1122; 9760</t>
+          <t>1125; 9671</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 4109</t>
+          <t>0; 4075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1356; 7020</t>
+          <t>1818; 8809</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>49281</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>72324</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2907; 14457</t>
+          <t>2979; 14692</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9266; 28163</t>
+          <t>9776; 27767</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12383; 32105</t>
+          <t>12605; 31835</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12427; 32778</t>
+          <t>14427; 35185</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3235; 15080</t>
+          <t>3238; 14612</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17003; 39836</t>
+          <t>17138; 38382</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13900; 34501</t>
+          <t>14526; 34650</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>32107; 56453</t>
+          <t>38129; 63449</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8652; 24923</t>
+          <t>8863; 25425</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>30317; 58695</t>
+          <t>31271; 59397</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30556; 58271</t>
+          <t>31829; 58698</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>49790; 80917</t>
+          <t>57944; 89819</t>
         </is>
       </c>
     </row>
